--- a/output_data/AC_Park_OG_Auto.xlsx
+++ b/output_data/AC_Park_OG_Auto.xlsx
@@ -437,122 +437,122 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126.045839365569</v>
+        <v>127.4755269219704</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100.0612300280494</v>
+        <v>99.27540547827498</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66.56683050686786</v>
+        <v>66.99149898561861</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>73.44578781496999</v>
+        <v>71.71947075527395</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>87.63135302239944</v>
+        <v>88.7311583489935</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>92.84386185507925</v>
+        <v>94.12620481748127</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>164.3760886430804</v>
+        <v>164.8525670243084</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>338.4843885866073</v>
+        <v>339.4348852315394</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>463.2149309879003</v>
+        <v>464.8347966432718</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>584.963890213487</v>
+        <v>593.0826103647456</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>558.8647321304243</v>
+        <v>553.3239979562796</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>549.1486812444271</v>
+        <v>534.3033480859986</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>525.8687740100014</v>
+        <v>531.2767572760623</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>553.3130980068132</v>
+        <v>550.5770400628699</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>549.4656023857663</v>
+        <v>547.5935559725499</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>508.7870597676897</v>
+        <v>517.865082129287</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>481.3513043957192</v>
+        <v>473.9423336420765</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>445.7031254427008</v>
+        <v>453.4193441630519</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>414.514784254584</v>
+        <v>422.0163577269623</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>387.0956280037905</v>
+        <v>380.8356404400846</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>327.8770962767575</v>
+        <v>327.7777185431258</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>280.8350192173322</v>
+        <v>292.1179107196848</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>233.9570922942397</v>
+        <v>238.0878765709355</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>197.7216644571128</v>
+        <v>202.6844976843636</v>
       </c>
     </row>
   </sheetData>
